--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487439_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487439_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7245</v>
+        <v>4.6189</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2828</v>
+        <v>2.4445</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4417</v>
+        <v>2.1743</v>
       </c>
       <c r="G2" t="n">
         <v>4.2028</v>
@@ -610,13 +610,13 @@
         <v>1.3709</v>
       </c>
       <c r="S2" t="n">
-        <v>1.318</v>
+        <v>1.2124</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1494</v>
+        <v>0.0123</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4674</v>
+        <v>1.2001</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2088</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2696</v>
+        <v>2.4522</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2865</v>
+        <v>0.6296</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9831</v>
+        <v>1.8227</v>
       </c>
       <c r="G3" t="n">
         <v>1.3599</v>
@@ -688,13 +688,13 @@
         <v>0.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7922</v>
+        <v>0.9748</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0081</v>
+        <v>0.3511</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7841</v>
+        <v>0.6237</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6659</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W. BURGOS CABRERA</t>
+          <t>A. CASAIS ROMERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6415</v>
+        <v>2.3804</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8659</v>
+        <v>1.916</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7756</v>
+        <v>0.4644</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1909</v>
+        <v>3.4413</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0768</v>
+        <v>0.0612</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.2677</v>
+        <v>3.38</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3175</v>
+        <v>4.7704</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4799</v>
+        <v>1.6893</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.1624</v>
+        <v>3.0812</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5084</v>
+        <v>-1.3292</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4031</v>
+        <v>-1.628</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1053</v>
+        <v>0.2988</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.546</v>
+        <v>-2.1543</v>
       </c>
       <c r="Q4" t="n">
         <v>-3.917</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3709</v>
+        <v>1.7626</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8787</v>
+        <v>0.4186</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4815</v>
+        <v>-0.0965</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3972</v>
+        <v>0.5151</v>
       </c>
       <c r="V4" t="n">
-        <v>2.4998</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>2.9839</v>
+        <v>1.159</v>
       </c>
       <c r="X4" t="n">
         <v>-0.4841</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. CASAIS ROMERO</t>
+          <t>W. BURGOS CABRERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6236</v>
+        <v>0.9918</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5067</v>
+        <v>-0.3027</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1169</v>
+        <v>1.2944</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4413</v>
+        <v>-0.1909</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0612</v>
+        <v>1.0768</v>
       </c>
       <c r="I5" t="n">
-        <v>3.38</v>
+        <v>-1.2677</v>
       </c>
       <c r="J5" t="n">
-        <v>4.7704</v>
+        <v>0.3175</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6893</v>
+        <v>1.4799</v>
       </c>
       <c r="L5" t="n">
-        <v>3.0812</v>
+        <v>-1.1624</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3292</v>
+        <v>-0.5084</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.628</v>
+        <v>-0.4031</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2988</v>
+        <v>-0.1053</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.1543</v>
+        <v>-2.546</v>
       </c>
       <c r="Q5" t="n">
         <v>-3.917</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7626</v>
+        <v>1.3709</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3382</v>
+        <v>1.2289</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5058</v>
+        <v>0.3129</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1676</v>
+        <v>0.916</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6749000000000001</v>
+        <v>2.4998</v>
       </c>
       <c r="W5" t="n">
-        <v>1.159</v>
+        <v>2.9839</v>
       </c>
       <c r="X5" t="n">
         <v>-0.4841</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1839</v>
+        <v>0.4812</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.05</v>
+        <v>-0.7859</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8661</v>
+        <v>1.2671</v>
       </c>
       <c r="G6" t="n">
         <v>-1.1693</v>
@@ -922,13 +922,13 @@
         <v>1.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5226</v>
+        <v>0.1425</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2682</v>
+        <v>-0.0041</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2544</v>
+        <v>0.1466</v>
       </c>
       <c r="V6" t="n">
         <v>0.3329</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9347</v>
+        <v>-0.0253</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.146</v>
+        <v>-2.3703</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2113</v>
+        <v>2.3449</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0446</v>
@@ -1000,13 +1000,13 @@
         <v>1.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1067</v>
+        <v>0.8027</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6534</v>
+        <v>0.1223</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5467</v>
+        <v>0.6803</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. IGLESIAS GONZALEZ</t>
+          <t>G. RUMSHA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.609</v>
+        <v>-2.5008</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.554</v>
+        <v>-2.8362</v>
       </c>
       <c r="F8" t="n">
-        <v>0.945</v>
+        <v>0.3353</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4238</v>
+        <v>-1.7782</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3678</v>
+        <v>-2.0511</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.056</v>
+        <v>0.2729</v>
       </c>
       <c r="J8" t="n">
-        <v>0.246</v>
+        <v>-1.3032</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4643</v>
+        <v>-1.3032</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2184</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6698</v>
+        <v>-0.475</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8322</v>
+        <v>-0.7479</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1624</v>
+        <v>0.2729</v>
       </c>
       <c r="P8" t="n">
         <v>-2.3502</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.917</v>
+        <v>-2.9377</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5668</v>
+        <v>0.5875</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0984</v>
+        <v>0.411</v>
       </c>
       <c r="T8" t="n">
-        <v>0.117</v>
+        <v>0.1882</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.2228</v>
       </c>
       <c r="V8" t="n">
-        <v>0.06660000000000001</v>
+        <v>1.2166</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X8" t="n">
-        <v>0.06660000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. RUMSHA</t>
+          <t>C. IGLESIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9415</v>
+        <v>-3.0275</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1432</v>
+        <v>-3.7587</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2017</v>
+        <v>0.7312</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7782</v>
+        <v>-1.4238</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0511</v>
+        <v>-1.3678</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2729</v>
+        <v>-0.056</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3032</v>
+        <v>0.246</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3032</v>
+        <v>0.4643</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.2184</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.475</v>
+        <v>-1.6698</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7479</v>
+        <v>-1.8322</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2729</v>
+        <v>0.1624</v>
       </c>
       <c r="P9" t="n">
         <v>-2.3502</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9377</v>
+        <v>-3.917</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5875</v>
+        <v>1.5668</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0297</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1188</v>
+        <v>-0.0876</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0891</v>
+        <v>0.7675</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2166</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.06660000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.0371</v>
+        <v>-4.5208</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1263</v>
+        <v>-2.7169</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9108</v>
+        <v>-1.8039</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9651999999999999</v>
@@ -1234,13 +1234,13 @@
         <v>0.9792</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6879999999999999</v>
+        <v>-0.1717</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8316</v>
+        <v>-0.4223</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1436</v>
+        <v>0.2506</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4254</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5530000000000008</v>
+        <v>0.8500999999999985</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.0776</v>
+        <v>-7.780600000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>8.630599999999999</v>
+        <v>8.6304</v>
       </c>
       <c r="G11" t="n">
         <v>3.431999999999999</v>
@@ -1312,10 +1312,10 @@
         <v>10.7715</v>
       </c>
       <c r="S11" t="n">
-        <v>5.4021</v>
+        <v>5.699099999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.07940000000000003</v>
+        <v>0.3763</v>
       </c>
       <c r="U11" t="n">
         <v>5.3227</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.6614</v>
+        <v>3.4743</v>
       </c>
       <c r="E12" t="n">
         <v>0.8075</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8538</v>
+        <v>2.6667</v>
       </c>
       <c r="G12" t="n">
         <v>2.2326</v>
@@ -1390,13 +1390,13 @@
         <v>1.5668</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2371</v>
+        <v>-0.4242</v>
       </c>
       <c r="T12" t="n">
         <v>-0.517</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2799</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>1.2742</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.1331</v>
+        <v>2.5901</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1225</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0106</v>
+        <v>1.8769</v>
       </c>
       <c r="G13" t="n">
         <v>0.4206</v>
@@ -1468,13 +1468,13 @@
         <v>3.5253</v>
       </c>
       <c r="S13" t="n">
-        <v>0.065</v>
+        <v>-0.478</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1623</v>
+        <v>-0.5717</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2273</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>0.4931</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5009</v>
+        <v>1.0113</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5776</v>
+        <v>1.1682</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0767</v>
+        <v>-0.1569</v>
       </c>
       <c r="G14" t="n">
         <v>0.07389999999999999</v>
@@ -1546,13 +1546,13 @@
         <v>3.5253</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0776</v>
+        <v>-0.5671</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1206</v>
+        <v>-0.5299</v>
       </c>
       <c r="U14" t="n">
-        <v>0.043</v>
+        <v>-0.0372</v>
       </c>
       <c r="V14" t="n">
         <v>-1.8249</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Y. REY CONDE</t>
+          <t>N. FUENTES PRADO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2517</v>
+        <v>0.7847</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.2282</v>
+        <v>-0.6303</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4799</v>
+        <v>1.415</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.478</v>
+        <v>-0.2072</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0429</v>
+        <v>-0.6158</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5209</v>
+        <v>0.4086</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.753</v>
+        <v>0.2574</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0408</v>
+        <v>0.3998</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7938</v>
+        <v>-0.1424</v>
       </c>
       <c r="M15" t="n">
-        <v>0.275</v>
+        <v>-0.4646</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0021</v>
+        <v>-1.0156</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2729</v>
+        <v>0.551</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.3709</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3709</v>
+        <v>2.3502</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6412</v>
+        <v>-1.4793</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4752</v>
+        <v>-1.0087</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.166</v>
+        <v>-0.4707</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. FUENTES PRADO</t>
+          <t>Y. REY CONDE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2279</v>
+        <v>0.5144</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7326</v>
+        <v>-1.1259</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9605</v>
+        <v>1.6403</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2072</v>
+        <v>-0.478</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6158</v>
+        <v>0.0429</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4086</v>
+        <v>-0.5209</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2574</v>
+        <v>-0.753</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3998</v>
+        <v>0.0408</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1424</v>
+        <v>-0.7938</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4646</v>
+        <v>0.275</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0156</v>
+        <v>0.0021</v>
       </c>
       <c r="O16" t="n">
-        <v>0.551</v>
+        <v>0.2729</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9792</v>
+        <v>1.3709</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.3709</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3502</v>
+        <v>1.3709</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.0361</v>
+        <v>-0.3785</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.111</v>
+        <v>-0.3729</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9251</v>
+        <v>-0.0056</v>
       </c>
       <c r="V16" t="n">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0528</v>
+        <v>0.3506</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0924</v>
+        <v>0.4192</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1452</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9419999999999999</v>
@@ -1780,13 +1780,13 @@
         <v>1.5668</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2967</v>
+        <v>0.0012</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8316</v>
+        <v>-0.3199</v>
       </c>
       <c r="U17" t="n">
-        <v>0.535</v>
+        <v>0.3211</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2754</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2446</v>
+        <v>-0.3515</v>
       </c>
       <c r="E18" t="n">
         <v>-1.1528</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9082</v>
+        <v>0.8013</v>
       </c>
       <c r="G18" t="n">
         <v>0.3546</v>
@@ -1858,13 +1858,13 @@
         <v>0.7834</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0299</v>
+        <v>-0.077</v>
       </c>
       <c r="T18" t="n">
         <v>-0.3564</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3863</v>
+        <v>0.2794</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2166</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. RODRÍGUEZ BLANCO</t>
+          <t>Y. PINAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.82</v>
+        <v>-1.7033</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1233</v>
+        <v>-1.5606</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3032</v>
+        <v>-0.1427</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.6211</v>
+        <v>-1.2035</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5751</v>
+        <v>-1.0626</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.046</v>
+        <v>-0.1409</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.945</v>
+        <v>1.2172</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.3032</v>
+        <v>0.9747</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6418</v>
+        <v>0.2425</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.676</v>
+        <v>-2.4207</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2719</v>
+        <v>-2.0373</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4042</v>
+        <v>-0.3834</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9792</v>
+        <v>0.5875</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.1543</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9792</v>
+        <v>2.7419</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1782</v>
+        <v>-0.8119</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1782</v>
+        <v>-0.6234</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.1885</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Y. PINAS</t>
+          <t>M. RODRÍGUEZ BLANCO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8591</v>
+        <v>-1.7177</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6629</v>
+        <v>-2.0209</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1962</v>
+        <v>0.3032</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2035</v>
+        <v>-2.6211</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0626</v>
+        <v>-1.5751</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1409</v>
+        <v>-1.046</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2172</v>
+        <v>-1.945</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9747</v>
+        <v>-1.3032</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2425</v>
+        <v>-0.6418</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.4207</v>
+        <v>-0.676</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.0373</v>
+        <v>-0.2719</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3834</v>
+        <v>-0.4042</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5875</v>
+        <v>0.9792</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1543</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7419</v>
+        <v>0.9792</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9677</v>
+        <v>-0.0759</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7258</v>
+        <v>-0.0759</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.242</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0021</v>
+        <v>-2.3313</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9672</v>
+        <v>-2.3766</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0349</v>
+        <v>0.0453</v>
       </c>
       <c r="G21" t="n">
         <v>1.8475</v>
@@ -2092,13 +2092,13 @@
         <v>2.1543</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7541</v>
+        <v>-1.0832</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4464</v>
+        <v>-0.8557</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3076</v>
+        <v>-0.2275</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9412</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4551</v>
+        <v>-3.1748</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9034</v>
+        <v>-2.5964</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5517</v>
+        <v>-0.5784</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9094</v>
@@ -2170,13 +2170,13 @@
         <v>0.9792</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3084</v>
+        <v>-0.0281</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3982</v>
+        <v>-0.0912</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0898</v>
+        <v>0.0631</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2166</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5530999999999993</v>
+        <v>-0.5531999999999995</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.3552</v>
+        <v>-8.355399999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>7.8019</v>
+        <v>7.802099999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-3.432</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6875</v>
+        <v>0.6874999999999996</v>
       </c>
       <c r="I23" t="n">
         <v>-4.1193</v>
@@ -2224,7 +2224,7 @@
         <v>5.593999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>7.796200000000001</v>
+        <v>7.796199999999999</v>
       </c>
       <c r="L23" t="n">
         <v>-2.2024</v>
@@ -2233,7 +2233,7 @@
         <v>-9.025700000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-7.109000000000001</v>
+        <v>-7.109</v>
       </c>
       <c r="O23" t="n">
         <v>-1.917</v>
@@ -2248,22 +2248,22 @@
         <v>21.5433</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.4022</v>
+        <v>-5.402</v>
       </c>
       <c r="T23" t="n">
         <v>-5.322699999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.07940000000000001</v>
+        <v>-0.07940000000000004</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.490799999999999</v>
+        <v>-2.4908</v>
       </c>
       <c r="W23" t="n">
         <v>2.1454</v>
       </c>
       <c r="X23" t="n">
-        <v>-4.6363</v>
+        <v>-4.636299999999999</v>
       </c>
     </row>
   </sheetData>
